--- a/results/05-2025/beta/inputs-05-2025.xlsx
+++ b/results/05-2025/beta/inputs-05-2025.xlsx
@@ -36089,7 +36089,7 @@
         <v>3175</v>
       </c>
       <c r="Q221" t="n">
-        <v>4514.4</v>
+        <v>4532.9</v>
       </c>
       <c r="R221" t="n">
         <v>2519.8</v>
@@ -36146,7 +36146,7 @@
         <v>289.625</v>
       </c>
       <c r="AJ221" t="n">
-        <v>-2622.27</v>
+        <v>-2624.49</v>
       </c>
       <c r="AK221" t="n">
         <v>-1450.014</v>
@@ -36205,37 +36205,37 @@
         <v>53</v>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D222" t="n">
-        <v>0.0133734190337964</v>
+        <v>0.0137243018229956</v>
       </c>
       <c r="E222" t="n">
-        <v>0.0117412234354819</v>
+        <v>0.0104105514461275</v>
       </c>
       <c r="F222" t="n">
-        <v>0.00612006850933144</v>
+        <v>0.00762609260571701</v>
       </c>
       <c r="G222" t="n">
-        <v>0.0106475310746721</v>
+        <v>0.00986485229844081</v>
       </c>
       <c r="H222" t="n">
-        <v>0.00888510419511879</v>
+        <v>0.00877263452176291</v>
       </c>
       <c r="I222" t="n">
         <v>0.00562014078474316</v>
       </c>
       <c r="J222" t="n">
-        <v>29977.6</v>
+        <v>29976.6</v>
       </c>
       <c r="K222" t="n">
-        <v>20526.3</v>
+        <v>20493.3</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>1925.3</v>
+        <v>1928.3</v>
       </c>
       <c r="N222" t="n">
         <v>424.254997</v>
@@ -36244,25 +36244,25 @@
         <v>79.275</v>
       </c>
       <c r="P222" t="n">
-        <v>3215.2</v>
+        <v>3220.1</v>
       </c>
       <c r="Q222" t="n">
-        <v>4610.4</v>
+        <v>4641.1</v>
       </c>
       <c r="R222" t="n">
-        <v>2542.3</v>
+        <v>2547.2</v>
       </c>
       <c r="S222" t="n">
-        <v>528.958231426876</v>
+        <v>507.7</v>
       </c>
       <c r="T222" t="n">
         <v>73.9806362924226</v>
       </c>
       <c r="U222" t="n">
-        <v>159.562778829061</v>
+        <v>170.9</v>
       </c>
       <c r="V222" t="n">
-        <v>2245.598</v>
+        <v>2262.998</v>
       </c>
       <c r="W222" t="n">
         <v>218.2</v>
@@ -36301,22 +36301,22 @@
         <v>1797.33</v>
       </c>
       <c r="AI222" t="n">
-        <v>319.57</v>
+        <v>318.97</v>
       </c>
       <c r="AJ222" t="n">
-        <v>-2656.296</v>
+        <v>-2662.2</v>
       </c>
       <c r="AK222" t="n">
-        <v>-1468.644</v>
+        <v>-1469.232</v>
       </c>
       <c r="AL222" t="n">
-        <v>-183.135274380896</v>
+        <v>-182.426666666667</v>
       </c>
       <c r="AM222" t="n">
-        <v>-65.118759294302</v>
+        <v>-65.4966666666666</v>
       </c>
       <c r="AN222" t="n">
-        <v>1958.21865</v>
+        <v>1962.13365</v>
       </c>
       <c r="AO222" t="n">
         <v>195.6825</v>
@@ -36352,7 +36352,7 @@
         <v>1574.482275</v>
       </c>
       <c r="AZ222" t="n">
-        <v>269.302725</v>
+        <v>269.167725</v>
       </c>
     </row>
     <row r="223">
@@ -36378,22 +36378,22 @@
         <v>0.00707611529348728</v>
       </c>
       <c r="H223" t="n">
-        <v>0.00680120911736926</v>
+        <v>0.00557412911254063</v>
       </c>
       <c r="I223" t="n">
         <v>0.00571780133544419</v>
       </c>
       <c r="J223" t="n">
-        <v>30286.4237665499</v>
+        <v>30285.4134647324</v>
       </c>
       <c r="K223" t="n">
-        <v>20766.8437570761</v>
+        <v>20733.4570364307</v>
       </c>
       <c r="L223" t="n">
         <v>-1</v>
       </c>
       <c r="M223" t="n">
-        <v>1925.02146598291</v>
+        <v>1928.03038116389</v>
       </c>
       <c r="N223" t="n">
         <v>419.738142682176</v>
@@ -36402,25 +36402,25 @@
         <v>75.203</v>
       </c>
       <c r="P223" t="n">
-        <v>3241.54452133217</v>
+        <v>3246.4846706711</v>
       </c>
       <c r="Q223" t="n">
-        <v>4663.34806810248</v>
+        <v>4717.22049262681</v>
       </c>
       <c r="R223" t="n">
-        <v>2562.75117872682</v>
+        <v>2567.71814278793</v>
       </c>
       <c r="S223" t="n">
-        <v>546.371432521478</v>
+        <v>524.413384291008</v>
       </c>
       <c r="T223" t="n">
         <v>88.3944428040623</v>
       </c>
       <c r="U223" t="n">
-        <v>159.49686908653</v>
+        <v>170.281780483501</v>
       </c>
       <c r="V223" t="n">
-        <v>2252.298</v>
+        <v>2269.698</v>
       </c>
       <c r="W223" t="n">
         <v>231.362463474923</v>
@@ -36456,25 +36456,25 @@
         <v>0</v>
       </c>
       <c r="AH223" t="n">
-        <v>1827.94383655349</v>
+        <v>1865.83476888355</v>
       </c>
       <c r="AI223" t="n">
-        <v>308.469678875928</v>
+        <v>318.967036828324</v>
       </c>
       <c r="AJ223" t="n">
-        <v>-2692.2837681723</v>
+        <v>-2703.54245911522</v>
       </c>
       <c r="AK223" t="n">
-        <v>-1486.29614144722</v>
+        <v>-1487.48017713455</v>
       </c>
       <c r="AL223" t="n">
-        <v>-187.444322131612</v>
+        <v>-186.003779476367</v>
       </c>
       <c r="AM223" t="n">
-        <v>-65.181988263853</v>
+        <v>-65.9193926827833</v>
       </c>
       <c r="AN223" t="n">
-        <v>1984.520925</v>
+        <v>1992.350925</v>
       </c>
       <c r="AO223" t="n">
         <v>199.994054281858</v>
@@ -36507,10 +36507,10 @@
         <v>0.28035</v>
       </c>
       <c r="AY223" t="n">
-        <v>1604.33681322453</v>
+        <v>1612.8622729988</v>
       </c>
       <c r="AZ223" t="n">
-        <v>271.986227747084</v>
+        <v>274.213133286373</v>
       </c>
     </row>
     <row r="224">
@@ -36542,16 +36542,16 @@
         <v>0.00573662843673683</v>
       </c>
       <c r="J224" t="n">
-        <v>30588.5491865933</v>
+        <v>30587.5288064032</v>
       </c>
       <c r="K224" t="n">
-        <v>20972.6791928678</v>
+        <v>20938.961551921</v>
       </c>
       <c r="L224" t="n">
         <v>-1</v>
       </c>
       <c r="M224" t="n">
-        <v>1930.59899124883</v>
+        <v>1933.61662441075</v>
       </c>
       <c r="N224" t="n">
         <v>422.424391696499</v>
@@ -36560,25 +36560,25 @@
         <v>75.203</v>
       </c>
       <c r="P224" t="n">
-        <v>3271.16884837732</v>
+        <v>3276.15414551499</v>
       </c>
       <c r="Q224" t="n">
-        <v>4686.66217076868</v>
+        <v>4740.83108394412</v>
       </c>
       <c r="R224" t="n">
-        <v>2589.75932297458</v>
+        <v>2594.78388182571</v>
       </c>
       <c r="S224" t="n">
-        <v>564.357872776274</v>
+        <v>541.676969910475</v>
       </c>
       <c r="T224" t="n">
         <v>103.083510693309</v>
       </c>
       <c r="U224" t="n">
-        <v>159.633396410345</v>
+        <v>170.427539556497</v>
       </c>
       <c r="V224" t="n">
-        <v>2258.998</v>
+        <v>2276.398</v>
       </c>
       <c r="W224" t="n">
         <v>234.744608694576</v>
@@ -36614,25 +36614,25 @@
         <v>0</v>
       </c>
       <c r="AH224" t="n">
-        <v>1856.50122664367</v>
+        <v>1895.08344536113</v>
       </c>
       <c r="AI224" t="n">
-        <v>313.70729612385</v>
+        <v>324.356006275935</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-2723.01722866454</v>
+        <v>-2738.93418918851</v>
       </c>
       <c r="AK224" t="n">
-        <v>-1503.48726020417</v>
+        <v>-1504.98024295364</v>
       </c>
       <c r="AL224" t="n">
-        <v>-192.849584557487</v>
+        <v>-190.653011806716</v>
       </c>
       <c r="AM224" t="n">
-        <v>-65.1997681441978</v>
+        <v>-66.2969773346665</v>
       </c>
       <c r="AN224" t="n">
-        <v>2008.5507</v>
+        <v>2020.2957</v>
       </c>
       <c r="AO224" t="n">
         <v>202.951591238137</v>
@@ -36665,10 +36665,10 @@
         <v>0.250425</v>
       </c>
       <c r="AY224" t="n">
-        <v>1632.47626421936</v>
+        <v>1649.68272320505</v>
       </c>
       <c r="AZ224" t="n">
-        <v>277.05869437495</v>
+        <v>281.681559698458</v>
       </c>
     </row>
     <row r="225">
@@ -36700,16 +36700,16 @@
         <v>0.00571666765914358</v>
       </c>
       <c r="J225" t="n">
-        <v>30881.6768277472</v>
+        <v>30880.6466693347</v>
       </c>
       <c r="K225" t="n">
-        <v>21171.3717567429</v>
+        <v>21137.3346790439</v>
       </c>
       <c r="L225" t="n">
         <v>-1</v>
       </c>
       <c r="M225" t="n">
-        <v>1936.41752255301</v>
+        <v>1939.44425040166</v>
       </c>
       <c r="N225" t="n">
         <v>421.251410497087</v>
@@ -36718,25 +36718,25 @@
         <v>75.203</v>
       </c>
       <c r="P225" t="n">
-        <v>3301.89915703369</v>
+        <v>3306.93128749819</v>
       </c>
       <c r="Q225" t="n">
-        <v>4710.1942189707</v>
+        <v>4764.66130170926</v>
       </c>
       <c r="R225" t="n">
-        <v>2616.35842214835</v>
+        <v>2621.44160796255</v>
       </c>
       <c r="S225" t="n">
-        <v>560.870776304892</v>
+        <v>538.330015891544</v>
       </c>
       <c r="T225" t="n">
         <v>109.658761987664</v>
       </c>
       <c r="U225" t="n">
-        <v>159.553363151557</v>
+        <v>170.342094582672</v>
       </c>
       <c r="V225" t="n">
-        <v>2249.459</v>
+        <v>2266.859</v>
       </c>
       <c r="W225" t="n">
         <v>238.176195410118</v>
@@ -36772,25 +36772,25 @@
         <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1883.94791898553</v>
+        <v>1923.08767585383</v>
       </c>
       <c r="AI225" t="n">
-        <v>319.891467598308</v>
+        <v>330.697079507339</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-2751.17765085487</v>
+        <v>-2770.39831583601</v>
       </c>
       <c r="AK225" t="n">
-        <v>-1520.93320013836</v>
+        <v>-1522.73814734187</v>
       </c>
       <c r="AL225" t="n">
-        <v>-197.98194376765</v>
+        <v>-195.034012336434</v>
       </c>
       <c r="AM225" t="n">
-        <v>-65.1115469159164</v>
+        <v>-66.5683804874222</v>
       </c>
       <c r="AN225" t="n">
-        <v>2026.429425</v>
+        <v>2042.089425</v>
       </c>
       <c r="AO225" t="n">
         <v>207.558735205414</v>
@@ -36823,10 +36823,10 @@
         <v>0.222075</v>
       </c>
       <c r="AY225" t="n">
-        <v>1657.28767099111</v>
+        <v>1683.30057527216</v>
       </c>
       <c r="AZ225" t="n">
-        <v>283.86864958457</v>
+        <v>290.92277758761</v>
       </c>
     </row>
     <row r="226">
@@ -36858,16 +36858,16 @@
         <v>0.00567994383495618</v>
       </c>
       <c r="J226" t="n">
-        <v>31184.5020750375</v>
+        <v>31183.4618149075</v>
       </c>
       <c r="K226" t="n">
-        <v>21352.559254231</v>
+        <v>21318.230882562</v>
       </c>
       <c r="L226" t="n">
         <v>-1</v>
       </c>
       <c r="M226" t="n">
-        <v>1946.5379849104</v>
+        <v>1949.5805316023</v>
       </c>
       <c r="N226" t="n">
         <v>424.1169988</v>
@@ -36876,25 +36876,25 @@
         <v>75.203</v>
       </c>
       <c r="P226" t="n">
-        <v>3333.5039285268</v>
+        <v>3338.58422500907</v>
       </c>
       <c r="Q226" t="n">
-        <v>4798.76217041658</v>
+        <v>4835.0576346839</v>
       </c>
       <c r="R226" t="n">
-        <v>2640.81900117566</v>
+        <v>2645.95677316753</v>
       </c>
       <c r="S226" t="n">
-        <v>557.405226164991</v>
+        <v>535.003742281468</v>
       </c>
       <c r="T226" t="n">
         <v>134.709036355557</v>
       </c>
       <c r="U226" t="n">
-        <v>159.746384540398</v>
+        <v>170.548167754838</v>
       </c>
       <c r="V226" t="n">
-        <v>2293.159653035</v>
+        <v>2314.345022084</v>
       </c>
       <c r="W226" t="n">
         <v>241.657946376297</v>
@@ -36930,25 +36930,25 @@
         <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1910.04909464</v>
+        <v>1949.70317175716</v>
       </c>
       <c r="AI226" t="n">
-        <v>327.943050543782</v>
+        <v>338.959045575199</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-2781.98538105874</v>
+        <v>-2802.31136696143</v>
       </c>
       <c r="AK226" t="n">
-        <v>-1538.72792090097</v>
+        <v>-1540.84792721243</v>
       </c>
       <c r="AL226" t="n">
-        <v>-202.085451306483</v>
+        <v>-198.390803745816</v>
       </c>
       <c r="AM226" t="n">
-        <v>-65.1464264005963</v>
+        <v>-66.9633194125835</v>
       </c>
       <c r="AN226" t="n">
-        <v>2037.13079693288</v>
+        <v>2053.6425049689</v>
       </c>
       <c r="AO226" t="n">
         <v>212.83677314008</v>
@@ -36981,10 +36981,10 @@
         <v>0.1953</v>
       </c>
       <c r="AY226" t="n">
-        <v>1682.6494672851</v>
+        <v>1717.58453891753</v>
       </c>
       <c r="AZ226" t="n">
-        <v>285.752585956921</v>
+        <v>295.420312842029</v>
       </c>
     </row>
     <row r="227">
@@ -37016,16 +37016,16 @@
         <v>0.0056310426470525</v>
       </c>
       <c r="J227" t="n">
-        <v>31486.4275444389</v>
+        <v>31485.3772126063</v>
       </c>
       <c r="K227" t="n">
-        <v>21548.3343070416</v>
+        <v>21513.691189084</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>1957.03703617777</v>
+        <v>1960.09599346835</v>
       </c>
       <c r="N227" t="n">
         <v>424.207822909464</v>
@@ -37034,25 +37034,25 @@
         <v>75.203</v>
       </c>
       <c r="P227" t="n">
-        <v>3362.97076974958</v>
+        <v>3368.09597402047</v>
       </c>
       <c r="Q227" t="n">
-        <v>4831.46058553563</v>
+        <v>4868.02257452384</v>
       </c>
       <c r="R227" t="n">
-        <v>2666.27438952133</v>
+        <v>2671.46566999164</v>
       </c>
       <c r="S227" t="n">
-        <v>553.961089224493</v>
+        <v>531.698021298596</v>
       </c>
       <c r="T227" t="n">
         <v>155.206844624839</v>
       </c>
       <c r="U227" t="n">
-        <v>160.061809736797</v>
+        <v>170.884921475207</v>
       </c>
       <c r="V227" t="n">
-        <v>2299.131653035</v>
+        <v>2320.317022084</v>
       </c>
       <c r="W227" t="n">
         <v>245.190594913367</v>
@@ -37088,25 +37088,25 @@
         <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>1942.02108715815</v>
+        <v>1982.28408664578</v>
       </c>
       <c r="AI227" t="n">
-        <v>330.653821723616</v>
+        <v>341.796006806908</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-2814.11699818478</v>
+        <v>-2835.56239780174</v>
       </c>
       <c r="AK227" t="n">
-        <v>-1555.35934231462</v>
+        <v>-1557.79731113367</v>
       </c>
       <c r="AL227" t="n">
-        <v>-206.237487613967</v>
+        <v>-201.800737789103</v>
       </c>
       <c r="AM227" t="n">
-        <v>-65.0684867251562</v>
+        <v>-67.2461501284237</v>
       </c>
       <c r="AN227" t="n">
-        <v>2047.66836886575</v>
+        <v>2065.0317849378</v>
       </c>
       <c r="AO227" t="n">
         <v>215.94810271373</v>
@@ -37139,10 +37139,10 @@
         <v>0.171675</v>
       </c>
       <c r="AY227" t="n">
-        <v>1708.31684867115</v>
+        <v>1743.78563541403</v>
       </c>
       <c r="AZ227" t="n">
-        <v>290.74401809765</v>
+        <v>300.556831087211</v>
       </c>
     </row>
     <row r="228">
@@ -37174,16 +37174,16 @@
         <v>0.00558696597638098</v>
       </c>
       <c r="J228" t="n">
-        <v>31781.7546426547</v>
+        <v>31780.6944592296</v>
       </c>
       <c r="K228" t="n">
-        <v>21719.4614215487</v>
+        <v>21684.5431836339</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>1968.29041439161</v>
+        <v>1971.36696133569</v>
       </c>
       <c r="N228" t="n">
         <v>428.130161044359</v>
@@ -37192,25 +37192,25 @@
         <v>75.203</v>
       </c>
       <c r="P228" t="n">
-        <v>3392.99282848061</v>
+        <v>3398.16378669769</v>
       </c>
       <c r="Q228" t="n">
-        <v>4864.53515129615</v>
+        <v>4901.36597331676</v>
       </c>
       <c r="R228" t="n">
-        <v>2689.50309192421</v>
+        <v>2694.74664119729</v>
       </c>
       <c r="S228" t="n">
-        <v>550.538233173925</v>
+        <v>528.412725950823</v>
       </c>
       <c r="T228" t="n">
         <v>162.820344255939</v>
       </c>
       <c r="U228" t="n">
-        <v>159.901743219221</v>
+        <v>170.714031527557</v>
       </c>
       <c r="V228" t="n">
-        <v>2306.831653035</v>
+        <v>2328.017022084</v>
       </c>
       <c r="W228" t="n">
         <v>248.77488506154</v>
@@ -37246,25 +37246,25 @@
         <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>1971.7310807032</v>
+        <v>2012.58716069019</v>
       </c>
       <c r="AI228" t="n">
-        <v>336.164833501387</v>
+        <v>347.459607178299</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-2842.54548611532</v>
+        <v>-2866.23285651872</v>
       </c>
       <c r="AK228" t="n">
-        <v>-1571.00057327499</v>
+        <v>-1573.75950168729</v>
       </c>
       <c r="AL228" t="n">
-        <v>-209.525428719764</v>
+        <v>-204.351161987464</v>
       </c>
       <c r="AM228" t="n">
-        <v>-64.8685448324636</v>
+        <v>-67.406617846009</v>
       </c>
       <c r="AN228" t="n">
-        <v>2058.43094079863</v>
+        <v>2076.6460649067</v>
       </c>
       <c r="AO228" t="n">
         <v>219.104914896297</v>
@@ -37297,10 +37297,10 @@
         <v>0.14805</v>
       </c>
       <c r="AY228" t="n">
-        <v>1734.24356583455</v>
+        <v>1770.22397136307</v>
       </c>
       <c r="AZ228" t="n">
-        <v>295.796964007596</v>
+        <v>305.755141290243</v>
       </c>
     </row>
     <row r="229">
@@ -37332,16 +37332,16 @@
         <v>0.00554760795794795</v>
       </c>
       <c r="J229" t="n">
-        <v>32078.5813706853</v>
+        <v>32077.5112856428</v>
       </c>
       <c r="K229" t="n">
-        <v>21913.3250015929</v>
+        <v>21878.0950904519</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>1978.34003974195</v>
+        <v>1981.43229480711</v>
       </c>
       <c r="N229" t="n">
         <v>430.081294164971</v>
@@ -37350,25 +37350,25 @@
         <v>75.203</v>
       </c>
       <c r="P229" t="n">
-        <v>3422.29135435309</v>
+        <v>3427.50696384436</v>
       </c>
       <c r="Q229" t="n">
-        <v>4897.98824678233</v>
+        <v>4935.09023284619</v>
       </c>
       <c r="R229" t="n">
-        <v>2714.67204167151</v>
+        <v>2719.96838425624</v>
       </c>
       <c r="S229" t="n">
-        <v>547.13652652134</v>
+        <v>525.147730030713</v>
       </c>
       <c r="T229" t="n">
         <v>160.445027356869</v>
       </c>
       <c r="U229" t="n">
-        <v>160.094764608062</v>
+        <v>170.920104699724</v>
       </c>
       <c r="V229" t="n">
-        <v>2314.531653035</v>
+        <v>2335.717022084</v>
       </c>
       <c r="W229" t="n">
         <v>252.41157173769</v>
@@ -37404,25 +37404,25 @@
         <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>2000.86969889776</v>
+        <v>2042.33403218289</v>
       </c>
       <c r="AI229" t="n">
-        <v>341.589082125147</v>
+        <v>353.059598162703</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-2869.55244059706</v>
+        <v>-2894.38832998883</v>
       </c>
       <c r="AK229" t="n">
-        <v>-1585.59675490429</v>
+        <v>-1588.67976759855</v>
       </c>
       <c r="AL229" t="n">
-        <v>-212.269979603809</v>
+        <v>-206.362752988487</v>
       </c>
       <c r="AM229" t="n">
-        <v>-64.6417036527323</v>
+        <v>-67.5406213359998</v>
       </c>
       <c r="AN229" t="n">
-        <v>2073.0722877315</v>
+        <v>2092.1391198756</v>
       </c>
       <c r="AO229" t="n">
         <v>222.307874570001</v>
@@ -37455,10 +37455,10 @@
         <v>0.124425</v>
       </c>
       <c r="AY229" t="n">
-        <v>1760.5509663148</v>
+        <v>1797.05440153711</v>
       </c>
       <c r="AZ229" t="n">
-        <v>300.678927276135</v>
+        <v>310.7867079877</v>
       </c>
     </row>
     <row r="230">
@@ -37490,16 +37490,16 @@
         <v>0.00550459474437348</v>
       </c>
       <c r="J230" t="n">
-        <v>32383.0062231116</v>
+        <v>32381.9259829915</v>
       </c>
       <c r="K230" t="n">
-        <v>22119.5628527038</v>
+        <v>22084.001374301</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>1988.00732771279</v>
+        <v>1991.11469328454</v>
       </c>
       <c r="N230" t="n">
         <v>433.061506</v>
@@ -37508,25 +37508,25 @@
         <v>75.203</v>
       </c>
       <c r="P230" t="n">
-        <v>3450.9503756126</v>
+        <v>3456.20966176602</v>
       </c>
       <c r="Q230" t="n">
-        <v>5064.61887790274</v>
+        <v>5103.15015371027</v>
       </c>
       <c r="R230" t="n">
-        <v>2741.27092843024</v>
+        <v>2746.62247499062</v>
       </c>
       <c r="S230" t="n">
-        <v>543.755838587262</v>
+        <v>521.90290811065</v>
       </c>
       <c r="T230" t="n">
         <v>146.435353395161</v>
       </c>
       <c r="U230" t="n">
-        <v>159.788755089168</v>
+        <v>170.593403329216</v>
       </c>
       <c r="V230" t="n">
-        <v>2361.51118408981</v>
+        <v>2386.56898567593</v>
       </c>
       <c r="W230" t="n">
         <v>256.101420894358</v>
@@ -37562,25 +37562,25 @@
         <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>2030.63180933154</v>
+        <v>2072.71310096789</v>
       </c>
       <c r="AI230" t="n">
-        <v>346.90748748179</v>
+        <v>358.556825889455</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-2908.81059686762</v>
+        <v>-2934.21839003506</v>
       </c>
       <c r="AK230" t="n">
-        <v>-1600.64108080047</v>
+        <v>-1603.75766612558</v>
       </c>
       <c r="AL230" t="n">
-        <v>-215.065174223384</v>
+        <v>-208.429516592176</v>
       </c>
       <c r="AM230" t="n">
-        <v>-64.2879954890379</v>
+        <v>-67.5470681136403</v>
       </c>
       <c r="AN230" t="n">
-        <v>2088.45138221883</v>
+        <v>2108.38951168378</v>
       </c>
       <c r="AO230" t="n">
         <v>225.557656336565</v>
@@ -37613,10 +37613,10 @@
         <v>0.1008</v>
       </c>
       <c r="AY230" t="n">
-        <v>1787.6820771204</v>
+        <v>1824.73163560952</v>
       </c>
       <c r="AZ230" t="n">
-        <v>304.945925587186</v>
+        <v>315.196208558407</v>
       </c>
     </row>
     <row r="231">
@@ -37648,10 +37648,10 @@
         <v>0.00545389484594594</v>
       </c>
       <c r="J231" t="n">
-        <v>32679.3330745373</v>
+        <v>32678.2429494747</v>
       </c>
       <c r="K231" t="n">
-        <v>22303.5672574266</v>
+        <v>22267.7099563302</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -37726,19 +37726,19 @@
         <v>0</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-2335.13041797453</v>
+        <v>-2355.07974650668</v>
       </c>
       <c r="AK231" t="n">
-        <v>-1283.99568757657</v>
+        <v>-1286.49647450293</v>
       </c>
       <c r="AL231" t="n">
-        <v>-198.618507556717</v>
+        <v>-191.982849925509</v>
       </c>
       <c r="AM231" t="n">
-        <v>-58.8213288223712</v>
+        <v>-62.0804014469737</v>
       </c>
       <c r="AN231" t="n">
-        <v>1571.14676028596</v>
+        <v>1586.31818171488</v>
       </c>
       <c r="AO231" t="n">
         <v>170.389772481057</v>
@@ -37771,10 +37771,10 @@
         <v>0.0819</v>
       </c>
       <c r="AY231" t="n">
-        <v>1350.72733250981</v>
+        <v>1378.71771611422</v>
       </c>
       <c r="AZ231" t="n">
-        <v>230.548815699373</v>
+        <v>238.292107026853</v>
       </c>
     </row>
     <row r="232">
@@ -37806,10 +37806,10 @@
         <v>0.00542022049047874</v>
       </c>
       <c r="J232" t="n">
-        <v>32979.2590375188</v>
+        <v>32978.1589074537</v>
       </c>
       <c r="K232" t="n">
-        <v>22488.0746812984</v>
+        <v>22451.9207488078</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37884,19 +37884,19 @@
         <v>0</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-1750.05355505425</v>
+        <v>-1764.44087224741</v>
       </c>
       <c r="AK232" t="n">
-        <v>-964.133872492278</v>
+        <v>-966.012093093953</v>
       </c>
       <c r="AL232" t="n">
-        <v>-182.181840890051</v>
+        <v>-175.546183258842</v>
       </c>
       <c r="AM232" t="n">
-        <v>-53.4013288223713</v>
+        <v>-56.6604014469737</v>
       </c>
       <c r="AN232" t="n">
-        <v>1052.10963835308</v>
+        <v>1062.51435174598</v>
       </c>
       <c r="AO232" t="n">
         <v>114.415423342211</v>
@@ -37929,10 +37929,10 @@
         <v>0.063</v>
       </c>
       <c r="AY232" t="n">
-        <v>907.087839351592</v>
+        <v>925.885604958926</v>
       </c>
       <c r="AZ232" t="n">
-        <v>154.911728161561</v>
+        <v>160.113695411736</v>
       </c>
     </row>
     <row r="233">
@@ -37964,10 +37964,10 @@
         <v>0.00537879404345354</v>
       </c>
       <c r="J233" t="n">
-        <v>33289.8823598466</v>
+        <v>33288.771867934</v>
       </c>
       <c r="K233" t="n">
-        <v>22685.8618107052</v>
+        <v>22649.3898971235</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -38042,19 +38042,19 @@
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-1467.44190191601</v>
+        <v>-1478.56119414486</v>
       </c>
       <c r="AK233" t="n">
-        <v>-807.152367163377</v>
+        <v>-808.725596616199</v>
       </c>
       <c r="AL233" t="n">
-        <v>-165.111840890051</v>
+        <v>-158.476183258842</v>
       </c>
       <c r="AM233" t="n">
-        <v>-47.9279954890379</v>
+        <v>-51.1870681136403</v>
       </c>
       <c r="AN233" t="n">
-        <v>531.340016420206</v>
+        <v>536.978021777085</v>
       </c>
       <c r="AO233" t="n">
         <v>57.6228197012306</v>
@@ -38087,10 +38087,10 @@
         <v>0.0441</v>
       </c>
       <c r="AY233" t="n">
-        <v>456.892157099597</v>
+        <v>466.360447717776</v>
       </c>
       <c r="AZ233" t="n">
-        <v>78.0541846834028</v>
+        <v>80.6752858251275</v>
       </c>
     </row>
     <row r="234">
@@ -38122,10 +38122,10 @@
         <v>0.00534192357811758</v>
       </c>
       <c r="J234" t="n">
-        <v>33603.1050405203</v>
+        <v>33601.98410005</v>
       </c>
       <c r="K234" t="n">
-        <v>22893.7093230931</v>
+        <v>22856.9032544074</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -38200,16 +38200,16 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-1179.51617169101</v>
+        <v>-1188.45773606382</v>
       </c>
       <c r="AK234" t="n">
-        <v>-648.703227092837</v>
+        <v>-649.968190226147</v>
       </c>
       <c r="AL234" t="n">
-        <v>-147.479899842488</v>
+        <v>-141.552849925509</v>
       </c>
       <c r="AM234" t="n">
-        <v>-42.6092361947359</v>
+        <v>-45.4904014469737</v>
       </c>
       <c r="AN234" t="n">
         <v>0</v>
@@ -38280,10 +38280,10 @@
         <v>0.00532158987529296</v>
       </c>
       <c r="J235" t="n">
-        <v>33908.7295967984</v>
+        <v>33907.5984612306</v>
       </c>
       <c r="K235" t="n">
-        <v>23099.1423435654</v>
+        <v>23062.006001539</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -38358,16 +38358,16 @@
         <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-889.628536558873</v>
+        <v>-896.376381592393</v>
       </c>
       <c r="AK235" t="n">
-        <v>-488.726763721557</v>
+        <v>-489.680250026649</v>
       </c>
       <c r="AL235" t="n">
-        <v>-129.267518758439</v>
+        <v>-124.072403782476</v>
       </c>
       <c r="AM235" t="n">
-        <v>-37.2926738918515</v>
+        <v>-39.8143420975236</v>
       </c>
       <c r="AN235" t="n">
         <v>0</v>
@@ -38438,10 +38438,10 @@
         <v>0.00528941636235492</v>
       </c>
       <c r="J236" t="n">
-        <v>34223.151981324</v>
+        <v>34222.0103571786</v>
       </c>
       <c r="K236" t="n">
-        <v>23315.6417853169</v>
+        <v>23278.1573785356</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -38516,16 +38516,16 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-597.756427481104</v>
+        <v>-602.294423193388</v>
       </c>
       <c r="AK236" t="n">
-        <v>-327.356578206105</v>
+        <v>-327.995451554812</v>
       </c>
       <c r="AL236" t="n">
-        <v>-110.455589665897</v>
+        <v>-106.01650478546</v>
       </c>
       <c r="AM236" t="n">
-        <v>-31.9715606781734</v>
+        <v>-34.1334241123071</v>
       </c>
       <c r="AN236" t="n">
         <v>0</v>
@@ -38596,10 +38596,10 @@
         <v>0.00524963654830413</v>
       </c>
       <c r="J237" t="n">
-        <v>34544.8725642821</v>
+        <v>34543.7202081041</v>
       </c>
       <c r="K237" t="n">
-        <v>23536.064776431</v>
+        <v>23498.2259970299</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -38674,16 +38674,16 @@
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-303.877132674164</v>
+        <v>-306.189009222617</v>
       </c>
       <c r="AK237" t="n">
-        <v>-164.476255705814</v>
+        <v>-164.797348499437</v>
       </c>
       <c r="AL237" t="n">
-        <v>-91.7598971224003</v>
+        <v>-88.0721709224082</v>
       </c>
       <c r="AM237" t="n">
-        <v>-26.6531152397882</v>
+        <v>-28.4553542928847</v>
       </c>
       <c r="AN237" t="n">
         <v>0</v>
@@ -38754,10 +38754,10 @@
         <v>0.00521033508596069</v>
       </c>
       <c r="J238" t="n">
-        <v>34872.0917898949</v>
+        <v>34870.9285182591</v>
       </c>
       <c r="K238" t="n">
-        <v>23766.4475466963</v>
+        <v>23728.2383824027</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -38838,10 +38838,10 @@
         <v>0</v>
       </c>
       <c r="AL238" t="n">
-        <v>-73.1797229169006</v>
+        <v>-70.2387128463593</v>
       </c>
       <c r="AM238" t="n">
-        <v>-21.3282357551083</v>
+        <v>-22.7704153677234</v>
       </c>
       <c r="AN238" t="n">
         <v>0</v>
@@ -38912,10 +38912,10 @@
         <v>0.00516756143130825</v>
       </c>
       <c r="J239" t="n">
-        <v>35202.4102504586</v>
+        <v>35201.23595998</v>
       </c>
       <c r="K239" t="n">
-        <v>24002.3635276012</v>
+        <v>23963.775082708</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -38996,10 +38996,10 @@
         <v>0</v>
       </c>
       <c r="AL239" t="n">
-        <v>-54.7143532760842</v>
+        <v>-52.5154454697394</v>
       </c>
       <c r="AM239" t="n">
-        <v>-15.992842097215</v>
+        <v>-17.0742513185499</v>
       </c>
       <c r="AN239" t="n">
         <v>0</v>
@@ -39070,10 +39070,10 @@
         <v>0.00510570215168871</v>
       </c>
       <c r="J240" t="n">
-        <v>35534.6282421211</v>
+        <v>35533.4428694347</v>
       </c>
       <c r="K240" t="n">
-        <v>24235.3619974416</v>
+        <v>24196.3989624126</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -39154,10 +39154,10 @@
         <v>0</v>
       </c>
       <c r="AL240" t="n">
-        <v>-36.3630788369534</v>
+        <v>-34.9016879380454</v>
       </c>
       <c r="AM240" t="n">
-        <v>-10.6627839899077</v>
+        <v>-11.3837836009646</v>
       </c>
       <c r="AN240" t="n">
         <v>0</v>
@@ -39228,10 +39228,10 @@
         <v>0.00504465278509314</v>
       </c>
       <c r="J241" t="n">
-        <v>35869.3456168084</v>
+        <v>35868.1490785393</v>
       </c>
       <c r="K241" t="n">
-        <v>24471.1773745166</v>
+        <v>24431.8352206282</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -39312,10 +39312,10 @@
         <v>0</v>
       </c>
       <c r="AL241" t="n">
-        <v>-18.1251946195754</v>
+        <v>-17.3967636036883</v>
       </c>
       <c r="AM241" t="n">
-        <v>-5.32629183630559</v>
+        <v>-5.68644677764053</v>
       </c>
       <c r="AN241" t="n">
         <v>0</v>
@@ -39386,10 +39386,10 @@
         <v>0.00499215850685553</v>
       </c>
       <c r="J242" t="n">
-        <v>36210.7613380023</v>
+        <v>36209.5534107054</v>
       </c>
       <c r="K242" t="n">
-        <v>24715.7452847851</v>
+        <v>24676.0099406463</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -39544,10 +39544,10 @@
         <v>0.00493645950017374</v>
       </c>
       <c r="J243" t="n">
-        <v>36558.7754303819</v>
+        <v>36557.555893947</v>
       </c>
       <c r="K243" t="n">
-        <v>24974.3977312271</v>
+        <v>24934.2465532198</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -39702,10 +39702,10 @@
         <v>0.00488530487992378</v>
       </c>
       <c r="J244" t="n">
-        <v>36900.1911515758</v>
+        <v>36898.9602261131</v>
       </c>
       <c r="K244" t="n">
-        <v>25230.6356857536</v>
+        <v>25190.072555641</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -39860,10 +39860,10 @@
         <v>0.00484625476688616</v>
       </c>
       <c r="J245" t="n">
-        <v>37249.3049724862</v>
+        <v>37248.0624012006</v>
       </c>
       <c r="K245" t="n">
-        <v>25493.7147007072</v>
+        <v>25452.7286201607</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -40018,10 +40018,10 @@
         <v>0.0048076557063792</v>
       </c>
       <c r="J246" t="n">
-        <v>37602.2178555945</v>
+        <v>37600.9635117559</v>
       </c>
       <c r="K246" t="n">
-        <v>25757.5985462993</v>
+        <v>25716.1882213977</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -40176,10 +40176,10 @@
         <v>0.00478086441968562</v>
       </c>
       <c r="J247" t="n">
-        <v>37959.2297268634</v>
+        <v>37957.9634737369</v>
       </c>
       <c r="K247" t="n">
-        <v>26028.1222446589</v>
+        <v>25986.2770005538</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -40334,10 +40334,10 @@
         <v>0.00473926501804089</v>
       </c>
       <c r="J248" t="n">
-        <v>38320.4405616141</v>
+        <v>38319.1622591296</v>
       </c>
       <c r="K248" t="n">
-        <v>26298.5453391886</v>
+        <v>26256.2653376203</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -40492,10 +40492,10 @@
         <v>0.00471315781573667</v>
       </c>
       <c r="J249" t="n">
-        <v>38685.8503598466</v>
+        <v>38684.559867934</v>
       </c>
       <c r="K249" t="n">
-        <v>26570.9805103146</v>
+        <v>26528.2625164803</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -40650,10 +40650,10 @@
         <v>0.00467984343253258</v>
       </c>
       <c r="J250" t="n">
-        <v>39054.8592696348</v>
+        <v>39053.5564682341</v>
       </c>
       <c r="K250" t="n">
-        <v>26846.0313810156</v>
+        <v>26802.8711896722</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -40808,10 +40808,10 @@
         <v>0.0046431744591946</v>
       </c>
       <c r="J251" t="n">
-        <v>39427.1673650158</v>
+        <v>39425.852144072</v>
       </c>
       <c r="K251" t="n">
-        <v>27124.4021781004</v>
+        <v>27080.7944518235</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -40966,10 +40966,10 @@
         <v>0.00460321336856051</v>
       </c>
       <c r="J252" t="n">
-        <v>39803.1745472736</v>
+        <v>39801.8467833917</v>
       </c>
       <c r="K252" t="n">
-        <v>27405.8916939093</v>
+        <v>27361.831418755</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -41124,10 +41124,10 @@
         <v>0.00457107075767049</v>
       </c>
       <c r="J253" t="n">
-        <v>40182.5808904452</v>
+        <v>40181.2404702351</v>
       </c>
       <c r="K253" t="n">
-        <v>27690.6005322721</v>
+        <v>27646.0825325563</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -41282,10 +41282,10 @@
         <v>0.00449893851450689</v>
       </c>
       <c r="J254" t="n">
-        <v>40562.9869868267</v>
+        <v>40561.6338769385</v>
       </c>
       <c r="K254" t="n">
-        <v>27977.6232587205</v>
+        <v>27932.6438144204</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -41440,10 +41440,10 @@
         <v>0.00453719183232471</v>
       </c>
       <c r="J255" t="n">
-        <v>40948.5917999</v>
+        <v>40947.2258269135</v>
       </c>
       <c r="K255" t="n">
-        <v>28269.9779881489</v>
+        <v>28224.5285270376</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -41598,10 +41598,10 @@
         <v>0.00452033241158278</v>
       </c>
       <c r="J256" t="n">
-        <v>41336.995921961</v>
+        <v>41335.6169924962</v>
       </c>
       <c r="K256" t="n">
-        <v>28565.7532477908</v>
+        <v>28519.828270704</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -41756,10 +41756,10 @@
         <v>0.00449275624446099</v>
       </c>
       <c r="J257" t="n">
-        <v>41727.6994764049</v>
+        <v>41726.3075137569</v>
       </c>
       <c r="K257" t="n">
-        <v>28863.6411878587</v>
+        <v>28817.2372982537</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -41914,10 +41914,10 @@
         <v>0.00446545931210318</v>
       </c>
       <c r="J258" t="n">
-        <v>42120.8024385526</v>
+        <v>42119.3973626813</v>
       </c>
       <c r="K258" t="n">
-        <v>29163.440600693</v>
+        <v>29116.5547255074</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -42072,10 +42072,10 @@
         <v>0.00443843729721394</v>
       </c>
       <c r="J259" t="n">
-        <v>42516.5047590462</v>
+        <v>42515.0864832416</v>
       </c>
       <c r="K259" t="n">
-        <v>29465.8557131024</v>
+        <v>29418.4836470928</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -42230,10 +42230,10 @@
         <v>0.00440811664554808</v>
       </c>
       <c r="J260" t="n">
-        <v>42914.9064132066</v>
+        <v>42913.4748474237</v>
       </c>
       <c r="K260" t="n">
-        <v>29771.9931672148</v>
+        <v>29724.1289259965</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
